--- a/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N72_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T6165_W0035F0003T0006Z000C1N72_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>65.39097704280609</v>
+        <v>10.62603376945599</v>
       </c>
       <c r="D2" t="n">
-        <v>41.10760354781635</v>
+        <v>6.679985576520156</v>
       </c>
       <c r="E2" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F2" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>60.10312022145784</v>
+        <v>9.766757035986899</v>
       </c>
       <c r="D3" t="n">
-        <v>39.42397747564291</v>
+        <v>6.406396339791974</v>
       </c>
       <c r="E3" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F3" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>5.548362326832562</v>
+        <v>0.9016088781102913</v>
       </c>
       <c r="D4" t="n">
-        <v>5.692102110048206</v>
+        <v>0.9249665928828336</v>
       </c>
       <c r="E4" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F4" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.47533105960357</v>
+        <v>2.027241297185579</v>
       </c>
       <c r="D5" t="n">
-        <v>12.95956160968812</v>
+        <v>2.10592876157432</v>
       </c>
       <c r="E5" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F5" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.58485853514788</v>
+        <v>4.320039511961531</v>
       </c>
       <c r="D6" t="n">
-        <v>28.44691479708555</v>
+        <v>4.622623654526403</v>
       </c>
       <c r="E6" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F6" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>43.02483091736506</v>
+        <v>6.991535024071823</v>
       </c>
       <c r="D7" t="n">
-        <v>45.07075301748215</v>
+        <v>7.32399736534085</v>
       </c>
       <c r="E7" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F7" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>111.9660430118692</v>
+        <v>18.19448198942874</v>
       </c>
       <c r="D8" t="n">
-        <v>112.7595840011903</v>
+        <v>18.32343240019343</v>
       </c>
       <c r="E8" t="n">
-        <v>33.95605871039799</v>
+        <v>5.517859540439672</v>
       </c>
       <c r="F8" t="n">
-        <v>32.42278642463946</v>
+        <v>5.268702794003913</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
